--- a/data/trans_orig/Q25_A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años desde que dejó de fumar</t>
+          <t>Tiempo medio en años desde que dejó de fumar (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 15,16</t>
+          <t>11,52; 15,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 15,24</t>
+          <t>11,36; 15,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,79; 15,45</t>
+          <t>11,74; 15,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,76; 19,5</t>
+          <t>15,85; 19,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,25</t>
+          <t>4,85; 8,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 9,05</t>
+          <t>5,48; 8,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 15,1</t>
+          <t>7,3; 15,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,96</t>
+          <t>10,68; 14,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,1</t>
+          <t>10,18; 13,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,08</t>
+          <t>10,08; 13,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,36</t>
+          <t>10,78; 14,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,73; 17,69</t>
+          <t>14,62; 17,59</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 12,27</t>
+          <t>9,34; 11,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,03</t>
+          <t>10,26; 13,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,79</t>
+          <t>10,89; 13,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 16,33</t>
+          <t>3,19; 16,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,89</t>
+          <t>5,72; 8,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,57</t>
+          <t>6,55; 9,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 12,56</t>
+          <t>8,59; 12,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,77</t>
+          <t>10,3; 14,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 10,84</t>
+          <t>8,51; 10,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 11,81</t>
+          <t>9,57; 11,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 12,96</t>
+          <t>10,68; 12,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,85</t>
+          <t>3,81; 14,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,34</t>
+          <t>8,53; 11,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,56</t>
+          <t>10,55; 14,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,71</t>
+          <t>10,9; 14,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,55</t>
+          <t>14,25; 18,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,11</t>
+          <t>4,36; 8,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,37</t>
+          <t>5,17; 7,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,67</t>
+          <t>6,86; 10,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 13,95</t>
+          <t>9,67; 13,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,31</t>
+          <t>7,77; 10,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 11,44</t>
+          <t>8,77; 11,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,67</t>
+          <t>9,75; 12,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,12; 16,46</t>
+          <t>13,35; 16,41</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 11,5</t>
+          <t>8,9; 11,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 12,87</t>
+          <t>9,81; 13,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 14,1</t>
+          <t>11,04; 14,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,3; 17,35</t>
+          <t>14,37; 17,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,8</t>
+          <t>5,67; 8,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,1</t>
+          <t>7,51; 11,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,52</t>
+          <t>6,3; 8,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,55</t>
+          <t>12,31; 16,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 10,08</t>
+          <t>8,11; 10,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 11,84</t>
+          <t>9,42; 11,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 11,53</t>
+          <t>9,47; 11,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,52</t>
+          <t>14,0; 16,53</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,55</t>
+          <t>10,16; 11,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,52 +1286,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 13,43</t>
+          <t>11,78; 13,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,69</t>
+          <t>6,12; 16,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,71</t>
+          <t>5,96; 7,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,49</t>
+          <t>6,97; 8,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,96</t>
+          <t>8,0; 10,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,76; 14,09</t>
+          <t>11,83; 14,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,24</t>
+          <t>9,11; 10,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,29</t>
+          <t>10,06; 11,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 12,03</t>
+          <t>10,7; 11,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,41</t>
+          <t>7,55; 15,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,65</t>
+          <t>17,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,15</t>
+          <t>16,3</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,19</t>
+          <t>11,54; 15,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,13</t>
+          <t>11,36; 15,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,35</t>
+          <t>11,77; 15,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 19,5</t>
+          <t>15,73; 19,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,38</t>
+          <t>4,93; 8,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,98</t>
+          <t>5,6; 9,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 15,58</t>
+          <t>7,09; 15,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 14,78</t>
+          <t>10,94; 15,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,11</t>
+          <t>10,02; 13,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,08; 13,32</t>
+          <t>10,1; 13,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 14,35</t>
+          <t>10,88; 14,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,62; 17,59</t>
+          <t>14,69; 17,72</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>15,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,0</t>
+          <t>11,97</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>14,53</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 11,97</t>
+          <t>9,33; 12,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 13,01</t>
+          <t>10,34; 13,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,82</t>
+          <t>11,02; 13,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 16,09</t>
+          <t>14,19; 17,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 8,92</t>
+          <t>5,69; 8,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,69</t>
+          <t>6,38; 9,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,42</t>
+          <t>8,54; 12,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,12</t>
+          <t>10,21; 14,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,75</t>
+          <t>8,57; 10,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 11,77</t>
+          <t>9,61; 11,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,95</t>
+          <t>10,72; 12,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 14,77</t>
+          <t>13,22; 15,8</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,47</t>
+          <t>16,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,61</t>
+          <t>12,06</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>14,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,31</t>
+          <t>8,51; 11,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,4</t>
+          <t>10,51; 14,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 14,62</t>
+          <t>10,83; 14,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 18,63</t>
+          <t>14,21; 18,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,54</t>
+          <t>4,64; 8,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,6</t>
+          <t>5,17; 7,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,55</t>
+          <t>6,98; 10,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,88</t>
+          <t>9,91; 14,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 10,2</t>
+          <t>7,76; 10,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,52</t>
+          <t>8,83; 11,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 12,56</t>
+          <t>9,8; 12,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 16,41</t>
+          <t>13,23; 16,43</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,91</t>
+          <t>15,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>13,46</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,24</t>
+          <t>14,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 11,43</t>
+          <t>8,9; 11,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 13,07</t>
+          <t>9,85; 13,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,02</t>
+          <t>11,03; 13,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 17,43</t>
+          <t>14,44; 17,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,66</t>
+          <t>5,72; 8,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,06</t>
+          <t>7,67; 10,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,63</t>
+          <t>6,2; 8,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 16,51</t>
+          <t>11,75; 15,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 10,03</t>
+          <t>8,09; 10,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 11,74</t>
+          <t>9,51; 11,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 11,62</t>
+          <t>9,47; 11,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 16,53</t>
+          <t>13,75; 16,07</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,17</t>
+          <t>16,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,71</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,37</t>
+          <t>14,99</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,62</t>
+          <t>10,16; 11,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,28; 12,97</t>
+          <t>11,25; 12,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 13,46</t>
+          <t>11,88; 13,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 16,65</t>
+          <t>15,37; 17,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,65</t>
+          <t>5,98; 7,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,6</t>
+          <t>6,84; 8,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,1</t>
+          <t>7,96; 9,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,03</t>
+          <t>11,68; 13,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,31</t>
+          <t>9,11; 10,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 11,27</t>
+          <t>10,03; 11,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,98</t>
+          <t>10,7; 12,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,33</t>
+          <t>14,35; 15,77</t>
         </is>
       </c>
     </row>
